--- a/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:53:12+00:00</t>
+    <t>2026-08-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:08:45+00:00</t>
+    <t>2026-08-20T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:24:46+00:00</t>
+    <t>2026-08-21T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="86">
   <si>
     <t>Property</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRMedicationLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -52,10 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T08:13:05+00:00</t>
+    <t>2026-08-23T21:45:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,145 +130,136 @@
     <t>FRLMMedication.identifyingCode[x]</t>
   </si>
   <si>
-    <t>ManufacturedProduct.manufacturedProduct.manufacturedMaterial.code</t>
+    <t>ManufacturedProduct.manufacturedMaterial.code</t>
   </si>
   <si>
     <t>FRLMMedication.classification</t>
   </si>
   <si>
-    <t>ManufacturedProduct.pharm:asSpecializedKind</t>
+    <t>ManufacturedProduct.manufacturedMaterial.asSpecializedKind</t>
   </si>
   <si>
     <t>FRLMMedication.productName</t>
   </si>
   <si>
-    <t>ManufacturedProduct.manufacturedProduct.manufacturedMaterial.name</t>
+    <t>ManufacturedProduct.manufacturedMaterial.name</t>
   </si>
   <si>
     <t>FRLMMedication.item.doseForm</t>
   </si>
   <si>
-    <t>ManufacturedProduct.manufacturedProduct.manufacturedMaterial.pharm:formCode</t>
+    <t>ManufacturedProduct.manufacturedMaterial.formCode</t>
   </si>
   <si>
     <t>FRLMMedication.item.ingredient.substance</t>
   </si>
   <si>
-    <t>ManufacturedProduct.pharm:ingredient.pharm:ingredient.pharm:code</t>
+    <t>ManufacturedProduct.manufacturedMaterial.ingredient.ingredient.code</t>
   </si>
   <si>
     <t>FRLMMedication.item.ingredient.strengthInfo.strength</t>
   </si>
   <si>
-    <t>ManufacturedProduct.pharm:ingredient.pharm:quantity</t>
+    <t>ManufacturedProduct.manufacturedMaterial.ingredient.quantity</t>
   </si>
   <si>
     <t>FRLMMedication.item.unitOfPresentation</t>
   </si>
   <si>
-    <t>related-to</t>
-  </si>
-  <si>
-    <t>ManufacturedProduct.pharm:asContent</t>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.formCode</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.amount</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine.capacityQuantity</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.packageType</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.asContent.containerPackagedMedicine</t>
+  </si>
+  <si>
+    <t>FRLMMedication.batch.lotNumber</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.lotNumberText</t>
+  </si>
+  <si>
+    <t>FRLMMedication.batch.expirationDate</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct.manufacturedMaterial.expirationTime</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-document|0.1.0</t>
+  </si>
+  <si>
+    <t>Medication</t>
+  </si>
+  <si>
+    <t>FRMedicationDocument</t>
+  </si>
+  <si>
+    <t>Medication.code</t>
+  </si>
+  <si>
+    <t>Medication.extension:classification</t>
+  </si>
+  <si>
+    <t>Medication.extension:productName</t>
+  </si>
+  <si>
+    <t>FRLMMedication.marketingAuthorisationHolder</t>
+  </si>
+  <si>
+    <t>Medication.manufacturer</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemReference</t>
+  </si>
+  <si>
+    <t>Medication.form</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.ingredient</t>
+  </si>
+  <si>
+    <t>Medication.ingredient</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.ingredient.isActive</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.isActive</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.ingredient.strengthInfo.basisOfStrengthSubstance</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.extension:basisOfStrengthSubstance</t>
+  </si>
+  <si>
+    <t>Medication.extension:unitOfPresentation</t>
   </si>
   <si>
     <t>FRLMMedication.item.containedQuantity</t>
   </si>
   <si>
-    <t>FRLMMedication.item.amount</t>
-  </si>
-  <si>
-    <t>FRLMMedication.item.packageType</t>
-  </si>
-  <si>
-    <t>ManufacturedProduct.pharm:asContent.pharm:containerPackagedMedicine</t>
-  </si>
-  <si>
-    <t>FRLMMedication.batch.lotNumber</t>
-  </si>
-  <si>
-    <t>ManufacturedProduct.manufacturedProduct.manufacturedMaterial.lotNumberText</t>
-  </si>
-  <si>
-    <t>FRLMMedication.batch.expirationDate</t>
-  </si>
-  <si>
-    <t>ManufacturedProduct.pharm:expirationTime</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-document|0.1.0</t>
-  </si>
-  <si>
-    <t>Medication</t>
-  </si>
-  <si>
-    <t>FRMedicationDocument</t>
-  </si>
-  <si>
-    <t>Medication.code</t>
-  </si>
-  <si>
-    <t>Medication.extension:classification</t>
-  </si>
-  <si>
-    <t>Medication.extension:productName</t>
-  </si>
-  <si>
-    <t>FRLMMedication.marketingAuthorisationHolder</t>
-  </si>
-  <si>
-    <t>Medication.manufacturer</t>
-  </si>
-  <si>
-    <t>FRLMMedication.item</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.itemReference</t>
-  </si>
-  <si>
-    <t>Medication.form</t>
-  </si>
-  <si>
-    <t>FRLMMedication.item.ingredient</t>
-  </si>
-  <si>
-    <t>Medication.ingredient</t>
-  </si>
-  <si>
-    <t>FRLMMedication.item.ingredient.isActive</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.isActive</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.itemCodeableConcept</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:substanceActive.strength</t>
-  </si>
-  <si>
-    <t>FRLMMedication.item.ingredient.strengthInfo.basisOfStrengthSubstance</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.strength.extension:basisOfStrengthSubstance</t>
-  </si>
-  <si>
-    <t>Medication.extension:unitOfPresentation</t>
-  </si>
-  <si>
     <t>Medication.extension:sizeOfItem</t>
   </si>
   <si>
     <t>Medication.amount</t>
-  </si>
-  <si>
-    <t>Medication.extension:packageType</t>
-  </si>
-  <si>
-    <t>FRLMMedication.device</t>
-  </si>
-  <si>
-    <t>Medication.extension:device</t>
   </si>
   <si>
     <t>FRLMMedication.characteristic</t>
@@ -443,79 +440,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -526,213 +527,200 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="E15" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -741,224 +729,224 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -968,77 +956,51 @@
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E20" s="2"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="E22" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-23T21:45:18+00:00</t>
+    <t>2026-08-24T13:13:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:13:01+00:00</t>
+    <t>2026-08-25T11:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:34:21+00:00</t>
+    <t>2026-08-25T11:56:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:56:50+00:00</t>
+    <t>2026-08-25T20:08:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRMedicationLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T20:08:46+00:00</t>
+    <t>2026-08-31T08:09:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
